--- a/output/pdf_financials_xlsx/BOGO.xlsx
+++ b/output/pdf_financials_xlsx/BOGO.xlsx
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.029363</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.633977</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.183238</v>
       </c>
     </row>
     <row r="35">
@@ -1248,19 +1248,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.029363</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.633977</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.183238</v>
       </c>
     </row>
     <row r="37">
@@ -1518,13 +1518,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.337664</v>
+        <v>0.308301</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.312161</v>
+        <v>0.678184</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.943185</v>
+        <v>0.759947</v>
       </c>
     </row>
     <row r="49">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">

--- a/output/pdf_financials_xlsx/BOGO.xlsx
+++ b/output/pdf_financials_xlsx/BOGO.xlsx
@@ -1081,13 +1081,13 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.092181</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.335056</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.236374</v>
       </c>
     </row>
     <row r="29">
@@ -1103,13 +1103,13 @@
         <v>-0.021332</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-16.344645</v>
+        <v>-16.252464</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-6.119888</v>
+        <v>-5.784832</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-14.872323</v>
+        <v>-14.635949</v>
       </c>
     </row>
     <row r="30">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-614.7162962062672</v>
+        <v>-581.0613692955644</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-393.2380754703511</v>
+        <v>-386.9881266996561</v>
       </c>
     </row>
     <row r="31">
@@ -2683,13 +2683,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.092181</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.335056</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.236374</v>
       </c>
     </row>
     <row r="101">
@@ -5482,7 +5482,11 @@
           <t>Depreciation of property, plant, and equipment 9</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -6443,7 +6447,11 @@
           <t>Depreciation of property, plant, and equipment 8</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BOGO.xlsx
+++ b/output/pdf_financials_xlsx/BOGO.xlsx
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>0</v>
@@ -1973,7 +1973,7 @@
         <v>0.000817</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.066302</v>
+        <v>0.112302</v>
       </c>
       <c r="D68" s="3" t="n">
         <v>0.804485</v>
